--- a/results/ntnu_walking_speeds.xlsx
+++ b/results/ntnu_walking_speeds.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,22 +446,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.79 [0.75, 0.83]</t>
+          <t>0.79 [0.74, 0.84]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.79 [0.75, 0.83]</t>
+          <t>0.79 [0.74, 0.84]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79 [0.75, 0.83]</t>
+          <t>0.79 [0.74, 0.84]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.79 [0.75, 0.83]</t>
+          <t>0.79 [0.74, 0.84]</t>
         </is>
       </c>
     </row>
@@ -474,127 +474,137 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.79 [0.75, 0.84]</t>
+          <t>0.79 [0.74, 0.85]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.65 [0.57, 0.73]</t>
+          <t>0.65 [0.55, 0.75]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 1.00]</t>
+          <t>0.98 [0.96, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>kappa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.66 [0.56, 0.75]</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.91 [0.87, 0.95]</t>
+          <t>0.66 [0.56, 0.75]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.59 [0.51, 0.68]</t>
+          <t>0.66 [0.56, 0.75]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.66 [0.56, 0.75]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.73 [0.66, 0.80]</t>
+          <t>0.91 [0.86, 0.96]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.80 [0.69, 0.90]</t>
+          <t>0.59 [0.49, 0.69]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 1.00]</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>816.38 ± 68.49</t>
+          <t>0.73 [0.65, 0.82]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>363.00 ± 36.92</t>
+          <t>0.80 [0.67, 0.92]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>299.48 ± 2.73</t>
+          <t>0.97 [0.94, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
+          <t>support</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>19593</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8712</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6888</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>816.38 ± 68.49</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>363.00 ± 36.92</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>299.48 ± 2.73</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>19593</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>8712</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>6888</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -605,6 +615,23 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" t="n">
         <v>24</v>
       </c>
     </row>

--- a/results/ntnu_walking_speeds.xlsx
+++ b/results/ntnu_walking_speeds.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Walking Speeds" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Walking Speeds matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -590,7 +591,9 @@
           <t>support_total</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
         <v>19593</v>
       </c>
@@ -607,7 +610,9 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>24</v>
       </c>
@@ -624,7 +629,9 @@
           <t>n_total</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>24</v>
+      </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
@@ -633,6 +640,463 @@
       </c>
       <c r="E10" t="n">
         <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19.08100118137023</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.795041715890426</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2916477238108381</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6718896828598294</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9181937489210227</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.06698380727744944</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.002790991969893727</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01167269412944666</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.007719938420091414</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1008717157571847</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.004202988156549362</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.002050815257023766</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.00333700482236619</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.005068971490732533</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.75114329559514</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1979643039831308</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2923882068264955</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.07449959239769666</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.321429015568565</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2398703626784426</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01042914620341055</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.04788815494100614</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.03113753729700898</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" t="n">
+        <v>22.34616783466451</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9715725145506307</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.07167207045490671</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9405791871339331</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>23</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2274931557923663</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.009891006773581143</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01074799786533746</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.005243223965018986</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0145387895821433</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>23</v>
+      </c>
+      <c r="D9" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1864686468646865</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008107332472377674</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02275508556052259</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01794736936116777</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.056294008337247</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2523455836807186</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1899275335765578</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1721462199318328</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3325449474296044</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3559693895886745</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.01483205789952811</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.02732080892325399</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.003295492076297228</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.02636862372275899</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.58773660207408</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7328223584197534</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1950691722416063</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6504518710754709</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8151928457640359</v>
       </c>
     </row>
   </sheetData>

--- a/results/ntnu_walking_speeds.xlsx
+++ b/results/ntnu_walking_speeds.xlsx
@@ -414,28 +414,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>shuffle</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>fast-walk</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>run</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>bicycle</t>
         </is>
       </c>
     </row>
@@ -447,22 +477,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.79 [0.74, 0.84]</t>
+          <t>0.81 [0.75, 0.87]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.79 [0.74, 0.84]</t>
+          <t>0.81 [0.75, 0.87]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79 [0.74, 0.84]</t>
+          <t>0.81 [0.75, 0.87]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.79 [0.74, 0.84]</t>
+          <t>0.81 [0.75, 0.87]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.81 [0.75, 0.87]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.81 [0.75, 0.87]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.81 [0.75, 0.87]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.81 [0.75, 0.87]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.81 [0.75, 0.87]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.81 [0.75, 0.87]</t>
         </is>
       </c>
     </row>
@@ -473,21 +533,31 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.79 [0.74, 0.85]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.65 [0.55, 0.75]</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.86 [0.79, 0.93]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.65 [0.53, 0.77]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.73 [0.62, 0.84]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.98 [0.96, 1.00]</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,22 +567,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.66 [0.56, 0.75]</t>
+          <t>0.75 [0.67, 0.82]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.66 [0.56, 0.75]</t>
+          <t>0.75 [0.67, 0.82]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.66 [0.56, 0.75]</t>
+          <t>0.75 [0.67, 0.82]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.66 [0.56, 0.75]</t>
+          <t>0.75 [0.67, 0.82]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.75 [0.67, 0.82]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.75 [0.67, 0.82]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.75 [0.67, 0.82]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.75 [0.67, 0.82]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.75 [0.67, 0.82]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.75 [0.67, 0.82]</t>
         </is>
       </c>
     </row>
@@ -523,21 +623,31 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.91 [0.86, 0.96]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.59 [0.49, 0.69]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.93 [0.89, 0.97]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.70 [0.58, 0.82]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.81 [0.72, 0.89]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -546,21 +656,31 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.73 [0.65, 0.82]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.80 [0.67, 0.92]</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.85 [0.76, 0.94]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.65 [0.52, 0.79]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.81 [0.67, 0.94]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>0.97 [0.94, 1.00]</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -569,21 +689,31 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>816.38 ± 68.49</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>363.00 ± 36.92</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>299.48 ± 2.73</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>405.08 ± 30.95</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>416.79 ± 55.27</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>365.75 ± 33.29</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>299.29 ± 2.82</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -595,13 +725,31 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>19593</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>8712</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6888</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9722</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10003</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8778</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7183</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -614,13 +762,31 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -639,6 +805,24 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" t="n">
         <v>24</v>
       </c>
     </row>
@@ -653,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,7 +895,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fast-walk</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -721,19 +905,19 @@
         <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>19.08100118137023</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.795041715890426</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2916477238108381</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6718896828598294</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9181937489210227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -744,7 +928,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -754,19 +938,19 @@
         <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06698380727744944</v>
+        <v>19.3262035872779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002790991969893727</v>
+        <v>0.8052584828032456</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01167269412944666</v>
+        <v>0.3183404374995214</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.6708351053064152</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007719938420091414</v>
+        <v>0.9396818603000761</v>
       </c>
     </row>
     <row r="4">
@@ -777,7 +961,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -787,19 +971,19 @@
         <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1008717157571847</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004202988156549362</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002050815257023766</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00333700482236619</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005068971490732533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -810,7 +994,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -820,162 +1004,162 @@
         <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>4.75114329559514</v>
+        <v>0.06698380727744944</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1979643039831308</v>
+        <v>0.002790991969893727</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2923882068264955</v>
+        <v>0.01167269412944666</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07449959239769666</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.321429015568565</v>
+        <v>0.007719938420091414</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fast-walk</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2398703626784426</v>
+        <v>0.0995687970218055</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01042914620341055</v>
+        <v>0.004148699875908562</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04788815494100614</v>
+        <v>0.00199078765193249</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.003308063976323383</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03113753729700898</v>
+        <v>0.004989335775493741</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>22.34616783466451</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9715725145506307</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07167207045490671</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9405791871339331</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2274931557923663</v>
+        <v>0.09314887018193843</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009891006773581143</v>
+        <v>0.003881202924247434</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01074799786533746</v>
+        <v>0.001917506008344796</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005243223965018986</v>
+        <v>0.003071511148873907</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0145387895821433</v>
+        <v>0.004690894699620962</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>stairs</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1864686468646865</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008107332472377674</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02275508556052259</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01794736936116777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fast-walk</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -985,32 +1169,32 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>6.056294008337247</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2523455836807186</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1899275335765578</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1721462199318328</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3325449474296044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
@@ -1018,30 +1202,30 @@
         <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4.414094938240913</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.1839206224267047</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.3195093464768005</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.04900365795755487</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.3188375868958545</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1051,52 +1235,976 @@
         <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3559693895886745</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01483205789952811</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02732080892325399</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.003295492076297228</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02636862372275899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5437778272504031</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0226574094687668</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.06805220345679022</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05139333477758646</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" t="n">
+        <v>23.22867251978209</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9678613549909203</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.07355963774541985</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9367998441415563</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9989228658402843</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2275496529675075</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.009481235540312813</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.01056620070663229</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.005019520285250238</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.01394295079537539</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" t="n">
+        <v>24</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>24</v>
+      </c>
+      <c r="D23" t="n">
+        <v>24</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.02027569555574272</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0008448206481559468</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.003208379263636187</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.002199600393689903</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>24</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="n">
+        <v>24</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2935931841427202</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.01223304933928001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.01111266415287421</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.007540582808321145</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.01692551587023887</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D28" t="n">
+        <v>24</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20.30242392120702</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8459343300502923</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.2136649526506092</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7557115333060413</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9361571267945432</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>24</v>
+      </c>
+      <c r="D29" t="n">
+        <v>24</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>24</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>24</v>
-      </c>
-      <c r="D13" t="n">
-        <v>24</v>
-      </c>
-      <c r="E13" t="n">
-        <v>17.58773660207408</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.7328223584197534</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.1950691722416063</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.6504518710754709</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.8151928457640359</v>
+      <c r="C31" t="n">
+        <v>24</v>
+      </c>
+      <c r="D31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.383707199094519</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1409877999622716</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.2124848028709172</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.05126333676491283</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2307122631596304</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>24</v>
+      </c>
+      <c r="D32" t="n">
+        <v>24</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>24</v>
+      </c>
+      <c r="D33" t="n">
+        <v>24</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.132934653901385</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.2555389439125577</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.3371092572445158</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1131901889124211</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3978876989126943</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>24</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>24</v>
+      </c>
+      <c r="D35" t="n">
+        <v>24</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>24</v>
+      </c>
+      <c r="D36" t="n">
+        <v>24</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.08052039921730408</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.003355016634054337</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.001996949650076751</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.002511778750853168</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.004198254517255506</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>24</v>
+      </c>
+      <c r="D37" t="n">
+        <v>24</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>24</v>
+      </c>
+      <c r="D38" t="n">
+        <v>24</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.118943615586685</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.08828931731611185</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1664588575958936</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.01799990630674993</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1585787283254738</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>24</v>
+      </c>
+      <c r="D39" t="n">
+        <v>24</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>24</v>
+      </c>
+      <c r="D40" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>24</v>
+      </c>
+      <c r="D41" t="n">
+        <v>24</v>
+      </c>
+      <c r="E41" t="n">
+        <v>15.66760133129463</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6528167221372762</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.3145439907111875</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5199964435234634</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7856370007510889</v>
       </c>
     </row>
   </sheetData>
